--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -5128,7 +5128,7 @@
         <v>136248783</v>
       </c>
       <c r="B39" t="n">
-        <v>86808</v>
+        <v>86810</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>136248878</v>
       </c>
       <c r="B40" t="n">
-        <v>86808</v>
+        <v>86810</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>136248885</v>
       </c>
       <c r="B41" t="n">
-        <v>86808</v>
+        <v>86810</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>136249039</v>
       </c>
       <c r="B42" t="n">
-        <v>86808</v>
+        <v>86810</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
         <v>136248749</v>
       </c>
       <c r="B3" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>136248998</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>78835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>136248766</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>136248747</v>
       </c>
       <c r="B6" t="n">
-        <v>79633</v>
+        <v>79635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>136248888</v>
       </c>
       <c r="B7" t="n">
-        <v>79633</v>
+        <v>79635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>136249008</v>
       </c>
       <c r="B8" t="n">
-        <v>79633</v>
+        <v>79635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>136248737</v>
       </c>
       <c r="B9" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136248746</v>
       </c>
       <c r="B10" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136248867</v>
       </c>
       <c r="B11" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136248981</v>
       </c>
       <c r="B12" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>136249063</v>
       </c>
       <c r="B13" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,32 +2136,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136249001</v>
+        <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>75433</v>
+        <v>80592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6428</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448501</v>
+        <v>448421</v>
       </c>
       <c r="R14" t="n">
-        <v>7180542</v>
+        <v>7180520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2224,17 +2224,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>gråal</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2251,38 +2251,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249001</t>
+          <t>https://artportalen.se/Sighting/136779198</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111335715</v>
+        <v>136249001</v>
       </c>
       <c r="B15" t="n">
-        <v>80432</v>
+        <v>75435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448695</v>
+        <v>448501</v>
       </c>
       <c r="R15" t="n">
-        <v>7180488</v>
+        <v>7180542</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2343,6 +2343,21 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2351,22 +2366,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111335715</t>
+          <t>https://artportalen.se/Sighting/136249001</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136248732</v>
+        <v>111335715</v>
       </c>
       <c r="B16" t="n">
-        <v>80589</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448387</v>
+        <v>448695</v>
       </c>
       <c r="R16" t="n">
-        <v>7180665</v>
+        <v>7180488</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2431,12 +2446,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,21 +2464,6 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2472,22 +2472,22 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248732</t>
+          <t>https://artportalen.se/Sighting/111335715</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136248802</v>
+        <v>136248732</v>
       </c>
       <c r="B17" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448385</v>
+        <v>448387</v>
       </c>
       <c r="R17" t="n">
-        <v>7180534</v>
+        <v>7180665</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2572,17 +2572,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gråal</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Alnus incana</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Alnus incana</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2599,16 +2599,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248802</t>
+          <t>https://artportalen.se/Sighting/136248732</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136248979</v>
+        <v>136248802</v>
       </c>
       <c r="B18" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448501</v>
+        <v>448385</v>
       </c>
       <c r="R18" t="n">
-        <v>7180542</v>
+        <v>7180534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,17 +2693,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gråal</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Alnus incana</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2720,16 +2720,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248979</t>
+          <t>https://artportalen.se/Sighting/136248802</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136249015</v>
+        <v>136248979</v>
       </c>
       <c r="B19" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448499</v>
+        <v>448501</v>
       </c>
       <c r="R19" t="n">
-        <v>7180505</v>
+        <v>7180542</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2814,17 +2814,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2841,16 +2841,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249015</t>
+          <t>https://artportalen.se/Sighting/136248979</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136249059</v>
+        <v>136249015</v>
       </c>
       <c r="B20" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448523</v>
+        <v>448499</v>
       </c>
       <c r="R20" t="n">
-        <v>7180480</v>
+        <v>7180505</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2935,17 +2935,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2962,38 +2962,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249059</t>
+          <t>https://artportalen.se/Sighting/136249015</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111335718</v>
+        <v>136249059</v>
       </c>
       <c r="B21" t="n">
-        <v>80461</v>
+        <v>80591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448695</v>
+        <v>448523</v>
       </c>
       <c r="R21" t="n">
-        <v>7180488</v>
+        <v>7180480</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3036,12 +3036,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,6 +3054,21 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -3062,22 +3077,22 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111335718</t>
+          <t>https://artportalen.se/Sighting/136249059</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136248769</v>
+        <v>111335718</v>
       </c>
       <c r="B22" t="n">
-        <v>80594</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3112,10 +3127,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448390</v>
+        <v>448695</v>
       </c>
       <c r="R22" t="n">
-        <v>7180651</v>
+        <v>7180488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3142,12 +3157,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3168,22 +3183,22 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Robin Isaksson, Martin Westberg, Måns Svensson, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248769</t>
+          <t>https://artportalen.se/Sighting/111335718</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136248850</v>
+        <v>136248769</v>
       </c>
       <c r="B23" t="n">
-        <v>80600</v>
+        <v>80596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,21 +3206,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3218,10 +3233,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448438</v>
+        <v>448390</v>
       </c>
       <c r="R23" t="n">
-        <v>7180620</v>
+        <v>7180651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3266,21 +3281,6 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3295,16 +3295,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248850</t>
+          <t>https://artportalen.se/Sighting/136248769</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136248865</v>
+        <v>136248850</v>
       </c>
       <c r="B24" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448463</v>
+        <v>448438</v>
       </c>
       <c r="R24" t="n">
-        <v>7180587</v>
+        <v>7180620</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3416,16 +3416,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248865</t>
+          <t>https://artportalen.se/Sighting/136248850</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136249041</v>
+        <v>136248865</v>
       </c>
       <c r="B25" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448521</v>
+        <v>448463</v>
       </c>
       <c r="R25" t="n">
-        <v>7180480</v>
+        <v>7180587</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3537,16 +3537,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249041</t>
+          <t>https://artportalen.se/Sighting/136248865</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136249066</v>
+        <v>136249041</v>
       </c>
       <c r="B26" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448523</v>
+        <v>448521</v>
       </c>
       <c r="R26" t="n">
         <v>7180480</v>
@@ -3658,16 +3658,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249066</t>
+          <t>https://artportalen.se/Sighting/136249041</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136248882</v>
+        <v>136249066</v>
       </c>
       <c r="B27" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3675,21 +3675,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448463</v>
+        <v>448523</v>
       </c>
       <c r="R27" t="n">
-        <v>7180587</v>
+        <v>7180480</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3779,33 +3779,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248882</t>
+          <t>https://artportalen.se/Sighting/136249066</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136249050</v>
+        <v>136248882</v>
       </c>
       <c r="B28" t="n">
-        <v>82389</v>
+        <v>80603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228723</v>
+        <v>6464</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Protounguicularia nephromatis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Zhurb. &amp; Zavarzin) Huhtinen et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3818,10 +3823,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448521</v>
+        <v>448463</v>
       </c>
       <c r="R28" t="n">
-        <v>7180480</v>
+        <v>7180587</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3895,16 +3900,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249050</t>
+          <t>https://artportalen.se/Sighting/136248882</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112648183</v>
+        <v>136249050</v>
       </c>
       <c r="B29" t="n">
-        <v>78390</v>
+        <v>82391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3912,21 +3917,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228748</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Skrovelmössing</t>
-        </is>
+        <v>228723</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sclerococcum lobariellum</t>
+          <t>Protounguicularia nephromatis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Diederich</t>
+          <t>(Zhurb. &amp; Zavarzin) Huhtinen et al.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3935,14 +3935,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2 km NNV Storliden, Lerdalen, biflöde Storlidfjällets sydsluttning, Jmt</t>
+          <t>Lerdalsälven, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448684</v>
+        <v>448521</v>
       </c>
       <c r="R29" t="n">
-        <v>7180467</v>
+        <v>7180480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3969,17 +3969,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På lunglav på sälg.</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3992,35 +3987,45 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Måns Svensson, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112648183</t>
+          <t>https://artportalen.se/Sighting/136249050</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136249182</v>
+        <v>112648183</v>
       </c>
       <c r="B30" t="n">
-        <v>78534</v>
+        <v>78390</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4051,14 +4056,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lerdalsälven, Jmt</t>
+          <t>2 km NNV Storliden, Lerdalen, biflöde Storlidfjällets sydsluttning, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448695</v>
+        <v>448684</v>
       </c>
       <c r="R30" t="n">
-        <v>7180488</v>
+        <v>7180467</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4085,12 +4090,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4103,72 +4113,57 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>lunglav</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Salix caprea # lunglav</t>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Robin Isaksson</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Måns Svensson, Ola Hammarström, Martin Westberg, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249182</t>
+          <t>https://artportalen.se/Sighting/112648183</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136249068</v>
+        <v>136249182</v>
       </c>
       <c r="B31" t="n">
-        <v>80609</v>
+        <v>78536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229504</v>
+        <v>228748</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skrovelmössing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Sclerococcum lobariellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Nyl.) Ertz &amp; Diederich</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4181,10 +4176,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448523</v>
+        <v>448695</v>
       </c>
       <c r="R31" t="n">
-        <v>7180480</v>
+        <v>7180488</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4231,17 +4226,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>lunglav</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea # lunglav</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4258,16 +4258,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249068</t>
+          <t>https://artportalen.se/Sighting/136249182</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136248786</v>
+        <v>136249068</v>
       </c>
       <c r="B32" t="n">
-        <v>81534</v>
+        <v>80611</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229558</v>
+        <v>229504</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkporlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pertusaria sommerfeltii</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Flörke ex Sommerf.) Fr.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448410</v>
+        <v>448523</v>
       </c>
       <c r="R32" t="n">
-        <v>7180655</v>
+        <v>7180480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4379,38 +4379,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248786</t>
+          <t>https://artportalen.se/Sighting/136249068</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136248724</v>
+        <v>136248786</v>
       </c>
       <c r="B33" t="n">
-        <v>75490</v>
+        <v>81536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229653</v>
+        <v>229558</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Njurlavsknapp</t>
+          <t>Barkporlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Plectocarpon nephromeum</t>
+          <t>Pertusaria sommerfeltii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Norman) R.Sant.</t>
+          <t>(Flörke ex Sommerf.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>448310</v>
+        <v>448410</v>
       </c>
       <c r="R33" t="n">
-        <v>7180611</v>
+        <v>7180655</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4500,16 +4500,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248724</t>
+          <t>https://artportalen.se/Sighting/136248786</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136248767</v>
+        <v>136248724</v>
       </c>
       <c r="B34" t="n">
-        <v>75490</v>
+        <v>75492</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>448390</v>
+        <v>448310</v>
       </c>
       <c r="R34" t="n">
-        <v>7180651</v>
+        <v>7180611</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4602,14 +4602,9 @@
           <t>Sorbus aucuparia</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>stuplav</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia # stuplav</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4626,16 +4621,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248767</t>
+          <t>https://artportalen.se/Sighting/136248724</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136248848</v>
+        <v>136248767</v>
       </c>
       <c r="B35" t="n">
-        <v>75490</v>
+        <v>75492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4670,10 +4665,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448438</v>
+        <v>448390</v>
       </c>
       <c r="R35" t="n">
-        <v>7180620</v>
+        <v>7180651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4728,9 +4723,14 @@
           <t>Sorbus aucuparia</t>
         </is>
       </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>stuplav</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus aucuparia # stuplav</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4747,16 +4747,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248848</t>
+          <t>https://artportalen.se/Sighting/136248767</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136249061</v>
+        <v>136248848</v>
       </c>
       <c r="B36" t="n">
-        <v>75490</v>
+        <v>75492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448523</v>
+        <v>448438</v>
       </c>
       <c r="R36" t="n">
-        <v>7180480</v>
+        <v>7180620</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4868,16 +4868,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249061</t>
+          <t>https://artportalen.se/Sighting/136248848</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136258295</v>
+        <v>136249061</v>
       </c>
       <c r="B37" t="n">
-        <v>75490</v>
+        <v>75492</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448338</v>
+        <v>448523</v>
       </c>
       <c r="R37" t="n">
-        <v>7180629</v>
+        <v>7180480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4956,11 +4956,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4974,14 +4970,9 @@
           <t>Sorbus aucuparia</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Nephroma</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia # Nephroma</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4998,38 +4989,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136258295</t>
+          <t>https://artportalen.se/Sighting/136249061</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136248733</v>
+        <v>136258295</v>
       </c>
       <c r="B38" t="n">
-        <v>80545</v>
+        <v>75492</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229748</v>
+        <v>229653</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Njurlavsknapp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Plectocarpon nephromeum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Norman) R.Sant.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5042,10 +5033,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448387</v>
+        <v>448338</v>
       </c>
       <c r="R38" t="n">
-        <v>7180665</v>
+        <v>7180629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5086,7 +5077,11 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5100,9 +5095,14 @@
           <t>Sorbus aucuparia</t>
         </is>
       </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Nephroma</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Sorbus aucuparia # Nephroma</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5119,33 +5119,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248733</t>
+          <t>https://artportalen.se/Sighting/136258295</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136248783</v>
+        <v>136779194</v>
       </c>
       <c r="B39" t="n">
-        <v>86810</v>
+        <v>75494</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229848</v>
+        <v>229654</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skrovellavsknapp</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Refractohilum galligenum</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>D.Hawksw.</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5158,10 +5163,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>448390</v>
+        <v>448421</v>
       </c>
       <c r="R39" t="n">
-        <v>7180651</v>
+        <v>7180520</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5188,12 +5193,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5208,17 +5213,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>skrovellav</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5235,33 +5240,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248783</t>
+          <t>https://artportalen.se/Sighting/136779194</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136248878</v>
+        <v>136248733</v>
       </c>
       <c r="B40" t="n">
-        <v>86810</v>
+        <v>80547</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229848</v>
+        <v>229748</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Refractohilum galligenum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>D.Hawksw.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5274,10 +5284,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448463</v>
+        <v>448387</v>
       </c>
       <c r="R40" t="n">
-        <v>7180587</v>
+        <v>7180665</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5324,17 +5334,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>luddlav</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5351,16 +5361,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248878</t>
+          <t>https://artportalen.se/Sighting/136248733</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136248885</v>
+        <v>136248783</v>
       </c>
       <c r="B41" t="n">
-        <v>86810</v>
+        <v>86812</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5390,10 +5400,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448460</v>
+        <v>448390</v>
       </c>
       <c r="R41" t="n">
-        <v>7180581</v>
+        <v>7180651</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5467,16 +5477,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248885</t>
+          <t>https://artportalen.se/Sighting/136248783</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136249039</v>
+        <v>136248878</v>
       </c>
       <c r="B42" t="n">
-        <v>86810</v>
+        <v>86812</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,10 +5516,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448521</v>
+        <v>448463</v>
       </c>
       <c r="R42" t="n">
-        <v>7180480</v>
+        <v>7180587</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5556,17 +5566,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>luddlav</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5583,33 +5593,33 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249039</t>
+          <t>https://artportalen.se/Sighting/136248878</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136248812</v>
+        <v>136248885</v>
       </c>
       <c r="B43" t="n">
-        <v>77103</v>
+        <v>86812</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6000458</v>
+        <v>229848</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Abrothallus lobariae</t>
+          <t>Refractohilum galligenum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Diederich &amp; Etayo) Diederich &amp; Ertz</t>
+          <t>D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5622,10 +5632,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448385</v>
+        <v>448460</v>
       </c>
       <c r="R43" t="n">
-        <v>7180534</v>
+        <v>7180581</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5666,32 +5676,23 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gråal</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Alnus incana</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>lunglav</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Alnus incana # lunglav</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5708,33 +5709,33 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248812</t>
+          <t>https://artportalen.se/Sighting/136248885</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136248818</v>
+        <v>136249039</v>
       </c>
       <c r="B44" t="n">
-        <v>77103</v>
+        <v>86812</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6000458</v>
+        <v>229848</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Abrothallus lobariae</t>
+          <t>Refractohilum galligenum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Diederich &amp; Etayo) Diederich &amp; Ertz</t>
+          <t>D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5747,10 +5748,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448377</v>
+        <v>448521</v>
       </c>
       <c r="R44" t="n">
-        <v>7180557</v>
+        <v>7180480</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5791,32 +5792,23 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gråal</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Alnus incana</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>lunglav</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Alnus incana # lunglav</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5833,16 +5825,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248818</t>
+          <t>https://artportalen.se/Sighting/136249039</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136259146</v>
+        <v>136248812</v>
       </c>
       <c r="B45" t="n">
-        <v>77103</v>
+        <v>77105</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5872,10 +5864,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448425</v>
+        <v>448385</v>
       </c>
       <c r="R45" t="n">
-        <v>7180600</v>
+        <v>7180534</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5916,7 +5908,11 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5954,16 +5950,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259146</t>
+          <t>https://artportalen.se/Sighting/136248812</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136248826</v>
+        <v>136248818</v>
       </c>
       <c r="B46" t="n">
-        <v>82655</v>
+        <v>77105</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5971,16 +5967,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6021661</v>
+        <v>6000458</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calycina lobariae</t>
+          <t>Abrothallus lobariae</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Etayo) Suija &amp; F.Jonss.</t>
+          <t>(Diederich &amp; Etayo) Diederich &amp; Ertz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6079,33 +6075,33 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248826</t>
+          <t>https://artportalen.se/Sighting/136248818</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136261692</v>
+        <v>136259146</v>
       </c>
       <c r="B47" t="n">
-        <v>85481</v>
+        <v>77105</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6331313</v>
+        <v>6000458</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Roselliniella nephromatis</t>
+          <t>Abrothallus lobariae</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+          <t>(Diederich &amp; Etayo) Diederich &amp; Ertz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6118,10 +6114,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448499</v>
+        <v>448425</v>
       </c>
       <c r="R47" t="n">
-        <v>7180505</v>
+        <v>7180600</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6166,6 +6162,26 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gråal</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>lunglav</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Alnus incana # lunglav</t>
+        </is>
+      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
@@ -6180,33 +6196,33 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136261692</t>
+          <t>https://artportalen.se/Sighting/136259146</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136248872</v>
+        <v>136248826</v>
       </c>
       <c r="B48" t="n">
-        <v>80491</v>
+        <v>82657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6331317</v>
+        <v>6021661</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rostania pallida</t>
+          <t>Calycina lobariae</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>A.Košuth. et al.</t>
+          <t>(Etayo) Suija &amp; F.Jonss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6219,10 +6235,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448463</v>
+        <v>448377</v>
       </c>
       <c r="R48" t="n">
-        <v>7180587</v>
+        <v>7180557</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6263,23 +6279,32 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gråal</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Alnus incana</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>lunglav</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Alnus incana # lunglav</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6296,33 +6321,33 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248872</t>
+          <t>https://artportalen.se/Sighting/136248826</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136249028</v>
+        <v>136261692</v>
       </c>
       <c r="B49" t="n">
-        <v>80491</v>
+        <v>85483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6331317</v>
+        <v>6331313</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rostania pallida</t>
+          <t>Roselliniella nephromatis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>A.Košuth. et al.</t>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6335,10 +6360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448521</v>
+        <v>448499</v>
       </c>
       <c r="R49" t="n">
-        <v>7180480</v>
+        <v>7180505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6383,21 +6408,6 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
@@ -6412,33 +6422,33 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249028</t>
+          <t>https://artportalen.se/Sighting/136261692</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136258291</v>
+        <v>136248872</v>
       </c>
       <c r="B50" t="n">
-        <v>77970</v>
+        <v>80493</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6332624</v>
+        <v>6331317</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Merismatium lobariae</t>
+          <t>Rostania pallida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Zhurb.</t>
+          <t>A.Košuth. et al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6451,10 +6461,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448338</v>
+        <v>448463</v>
       </c>
       <c r="R50" t="n">
-        <v>7180629</v>
+        <v>7180587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6495,11 +6505,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6513,14 +6519,9 @@
           <t>Sorbus aucuparia</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>nephroma</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia # nephroma</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6536,6 +6537,247 @@
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248872</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136249028</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6331317</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Rostania pallida</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>A.Košuth. et al.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>448521</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7180480</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249028</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136258291</v>
+      </c>
+      <c r="B52" t="n">
+        <v>77972</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6332624</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Merismatium lobariae</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Zhurb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>448338</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7180629</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>nephroma</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # nephroma</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136258291</t>
         </is>
@@ -6592,6 +6834,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -6663,7 +6663,7 @@
         <v>136258291</v>
       </c>
       <c r="B52" t="n">
-        <v>77972</v>
+        <v>77966</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5370,7 +5370,7 @@
         <v>136248783</v>
       </c>
       <c r="B41" t="n">
-        <v>86812</v>
+        <v>86814</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>136248878</v>
       </c>
       <c r="B42" t="n">
-        <v>86812</v>
+        <v>86814</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>136248885</v>
       </c>
       <c r="B43" t="n">
-        <v>86812</v>
+        <v>86814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>136249039</v>
       </c>
       <c r="B44" t="n">
-        <v>86812</v>
+        <v>86814</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6327,10 +6327,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136261692</v>
+        <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>85483</v>
+        <v>79872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6338,16 +6338,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6331313</v>
+        <v>6331241</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Roselliniella nephromatis</t>
+          <t>Bacidina circumpulla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
+          <t>S.Ekman &amp; T.Sprib.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6356,14 +6356,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lerdalsälven, Jmt</t>
+          <t>Lerdalsälven , Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448499</v>
+        <v>448369</v>
       </c>
       <c r="R49" t="n">
-        <v>7180505</v>
+        <v>7180526</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6390,12 +6390,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6404,9 +6404,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>viden</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6416,39 +6435,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Robin Isaksson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136261692</t>
+          <t>https://artportalen.se/Sighting/136901388</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136248872</v>
+        <v>136261692</v>
       </c>
       <c r="B50" t="n">
-        <v>80493</v>
+        <v>85483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6331317</v>
+        <v>6331313</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rostania pallida</t>
+          <t>Roselliniella nephromatis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>A.Košuth. et al.</t>
+          <t>(P.Crouan &amp; H.Crouan) Matzer &amp; Hafellner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6461,10 +6480,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448463</v>
+        <v>448499</v>
       </c>
       <c r="R50" t="n">
-        <v>7180587</v>
+        <v>7180505</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6509,21 +6528,6 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
@@ -6538,13 +6542,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136248872</t>
+          <t>https://artportalen.se/Sighting/136261692</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136249028</v>
+        <v>136248872</v>
       </c>
       <c r="B51" t="n">
         <v>80493</v>
@@ -6577,10 +6581,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448521</v>
+        <v>448463</v>
       </c>
       <c r="R51" t="n">
-        <v>7180480</v>
+        <v>7180587</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6654,33 +6658,33 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136249028</t>
+          <t>https://artportalen.se/Sighting/136248872</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136258291</v>
+        <v>136249028</v>
       </c>
       <c r="B52" t="n">
-        <v>77966</v>
+        <v>80493</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6332624</v>
+        <v>6331317</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Merismatium lobariae</t>
+          <t>Rostania pallida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Zhurb.</t>
+          <t>A.Košuth. et al.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6693,10 +6697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448338</v>
+        <v>448521</v>
       </c>
       <c r="R52" t="n">
-        <v>7180629</v>
+        <v>7180480</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6737,11 +6741,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6755,14 +6755,9 @@
           <t>Sorbus aucuparia</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>nephroma</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia # nephroma</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6778,6 +6773,131 @@
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136249028</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136258291</v>
+      </c>
+      <c r="B53" t="n">
+        <v>77966</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6332624</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Merismatium lobariae</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Zhurb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lerdalsälven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>448338</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7180629</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>nephroma</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # nephroma</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136258291</t>
         </is>
@@ -6836,6 +6956,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Robin Isaksson, Karl Soler Kinnerbäck</t>
+          <t>Karl Soler Kinnerbäck, Robin Isaksson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>136248812</v>
       </c>
       <c r="B45" t="n">
-        <v>77105</v>
+        <v>77104</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79872</v>
+        <v>79876</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79876</v>
+        <v>79878</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79878</v>
+        <v>79876</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79876</v>
+        <v>79878</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79878</v>
+        <v>79881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136779194</v>
       </c>
       <c r="B39" t="n">
-        <v>75494</v>
+        <v>75507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79881</v>
+        <v>79894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136779194</v>
       </c>
       <c r="B39" t="n">
-        <v>75507</v>
+        <v>75509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79894</v>
+        <v>79896</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136779194</v>
       </c>
       <c r="B39" t="n">
-        <v>75509</v>
+        <v>75519</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79896</v>
+        <v>79906</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -2139,7 +2139,7 @@
         <v>136779198</v>
       </c>
       <c r="B14" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>136779194</v>
       </c>
       <c r="B39" t="n">
-        <v>75519</v>
+        <v>75522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79906</v>
+        <v>79909</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79909</v>
+        <v>79914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79914</v>
+        <v>79925</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79925</v>
+        <v>79926</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 536-2023 artfynd.xlsx
+++ b/artfynd/A 536-2023 artfynd.xlsx
@@ -6330,7 +6330,7 @@
         <v>136901388</v>
       </c>
       <c r="B49" t="n">
-        <v>79926</v>
+        <v>79928</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
